--- a/ES_S.xlsx
+++ b/ES_S.xlsx
@@ -56,12 +56,12 @@
   <dimension ref="A1:A1204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.7265625" customWidth="true"/>
+    <col min="1" max="1" width="15.88671875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0">
-        <v>0</v>
+        <v>2.7755575615628914e-17</v>
       </c>
     </row>
     <row r="2">
@@ -81,27 +81,27 @@
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>3.4694469519536142e-17</v>
+        <v>3.1225022567582528e-17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>-0.2995972804956622</v>
+        <v>-0.29959728049566225</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>2.7755575615628914e-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>0.135689586789221</v>
+        <v>0.13568958678922097</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>2.7755575615628914e-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -121,12 +121,12 @@
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>-9.7144514654701197e-17</v>
+        <v>-1.0408340855860843e-16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>0.22857142857142856</v>
+        <v>0.22857142857142854</v>
       </c>
     </row>
     <row r="15">
@@ -146,7 +146,7 @@
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>0.035641677146881968</v>
+        <v>0.035641677146881975</v>
       </c>
     </row>
     <row r="19">
@@ -161,7 +161,7 @@
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>1.457167719820518e-16</v>
+        <v>1.5959455978986625e-16</v>
       </c>
     </row>
     <row r="22">
@@ -171,17 +171,17 @@
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>-2.1076890233118206e-16</v>
+        <v>-2.2377932840100812e-16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>0.056400715721003386</v>
+        <v>0.0564007157210034</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>1.4918621893400541e-16</v>
+        <v>1.474514954580286e-16</v>
       </c>
     </row>
     <row r="26">
@@ -191,52 +191,52 @@
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>-6.2450045135165055e-17</v>
+        <v>-7.0256300777060687e-17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>1.3204033600627036e-16</v>
+        <v>1.4443121797753327e-16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>-1.4224732503009818e-16</v>
+        <v>-1.3183898417423734e-16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>-0.014798883522330082</v>
+        <v>-0.0147988835223301</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>1.3877787807814457e-16</v>
+        <v>1.4398204850607499e-16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>0.042300536790752269</v>
+        <v>0.042300536790752283</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>-1.5135462327897642e-16</v>
+        <v>-1.7694179454963432e-16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>-0.052870108322763731</v>
+        <v>-0.052870108322763745</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>2.1510571102112408e-16</v>
+        <v>2.0816681711721685e-16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>0.030153241508715553</v>
+        <v>0.03015324150871556</v>
       </c>
     </row>
     <row r="37">
@@ -246,7 +246,7 @@
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>0.016882899701154603</v>
+        <v>0.016882899701154586</v>
       </c>
     </row>
     <row r="39">
@@ -256,12 +256,12 @@
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>-0.060978346790446294</v>
+        <v>-0.060978346790446288</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>4.4929338027799304e-16</v>
+        <v>4.4408920985006262e-16</v>
       </c>
     </row>
     <row r="42">
@@ -271,12 +271,12 @@
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>-2.2898349882893854e-16</v>
+        <v>-2.4112656316077619e-16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>-0.055434860718587248</v>
+        <v>-0.055434860718587241</v>
       </c>
     </row>
     <row r="45">
@@ -286,17 +286,17 @@
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>0.013946743231388295</v>
+        <v>0.01394674323138829</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>1.7347234759768071e-16</v>
+        <v>1.8041124150158794e-16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>0.022614931131536901</v>
+        <v>0.022614931131536897</v>
       </c>
     </row>
     <row r="49">
@@ -311,57 +311,57 @@
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>1.7650811368064012e-16</v>
+        <v>1.7824283715661693e-16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>0.026031099563539956</v>
+        <v>0.026031099563539949</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>-4.7704895589362195e-17</v>
+        <v>-4.4235448637408581e-17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>-0.0082216019568498791</v>
+        <v>-0.0082216019568498826</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>5.3342746886286818e-17</v>
+        <v>6.0281640790194047e-17</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>-2.0348151487183308e-16</v>
+        <v>-1.9941575672501244e-16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>3.430415673744136e-16</v>
+        <v>3.4087316302944259e-16</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>-0.0076545949253426938</v>
+        <v>-0.0076545949253427076</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>-3.7296554733501353e-16</v>
+        <v>-3.6949610038305991e-16</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>0.022560286288401121</v>
+        <v>0.022560286288401104</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>5.5511151231257827e-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -386,17 +386,17 @@
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>-0.41943619269392707</v>
+        <v>-0.41943619269392701</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>-2.7755575615628914e-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>0.18996542150490939</v>
+        <v>0.18996542150490936</v>
       </c>
     </row>
     <row r="69">
@@ -406,7 +406,7 @@
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>0.089817026410141693</v>
+        <v>0.089817026410141665</v>
       </c>
     </row>
     <row r="71">
@@ -431,7 +431,7 @@
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>1.7347234759768071e-16</v>
+        <v>1.5959455978986625e-16</v>
       </c>
     </row>
     <row r="76">
@@ -446,7 +446,7 @@
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>0.049898348005634793</v>
+        <v>0.049898348005634766</v>
       </c>
     </row>
     <row r="79">
@@ -461,17 +461,17 @@
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>2.0816681711721685e-16</v>
+        <v>2.0122792321330962e-16</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>-0.11439168891652551</v>
+        <v>-0.11439168891652549</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>-2.8536201179818477e-16</v>
+        <v>-2.7495367094232392e-16</v>
       </c>
     </row>
     <row r="84">
@@ -486,82 +486,82 @@
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>-0.023905888766840938</v>
+        <v>-0.023905888766840962</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>-8.5001450322863548e-17</v>
+        <v>-1.0408340855860843e-16</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>1.6059744679941537e-16</v>
+        <v>1.7918376975630972e-16</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>-2.0643209364124004e-16</v>
+        <v>-1.960237527853792e-16</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>-0.02071843693126213</v>
+        <v>-0.020718436931262137</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>2.0643209364124004e-16</v>
+        <v>2.1337098754514727e-16</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>0.059220751507053193</v>
+        <v>0.059220751507053221</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>-2.3678975447083417e-16</v>
+        <v>-2.3245294578089215e-16</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>-0.07401815165186923</v>
+        <v>-0.074018151651869243</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>2.9143354396410359e-16</v>
+        <v>3.1225022567582528e-16</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>0.042214538112201772</v>
+        <v>0.042214538112201785</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>-6.9388939039072284e-18</v>
+        <v>-2.0816681711721685e-17</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>0.023636059581616416</v>
+        <v>0.023636059581616419</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>-2.4980018054066022e-16</v>
+        <v>-2.3592239273284576e-16</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>-0.085369685506624798</v>
+        <v>-0.085369685506624812</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0">
-        <v>6.349087922075114e-16</v>
+        <v>6.2796989830360417e-16</v>
       </c>
     </row>
     <row r="102">
@@ -571,47 +571,47 @@
     </row>
     <row r="103">
       <c r="A103" s="0">
-        <v>-3.3306690738754696e-16</v>
+        <v>-3.4000580129145419e-16</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0">
-        <v>-0.07760880500602213</v>
+        <v>-0.077608805006022158</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0">
-        <v>3.3306690738754696e-16</v>
+        <v>3.1918911957973251e-16</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0">
-        <v>0.019525440523943612</v>
+        <v>0.019525440523943633</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0">
-        <v>2.7755575615628914e-16</v>
+        <v>2.8449465006019636e-16</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0">
-        <v>0.031660903584151676</v>
+        <v>0.031660903584151662</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0">
-        <v>-4.8572257327350599e-16</v>
+        <v>-4.8225312632155237e-16</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0">
-        <v>-0.050332343123271589</v>
+        <v>-0.050332343123271603</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0">
-        <v>2.3375398838787476e-16</v>
+        <v>2.4329496750574719e-16</v>
       </c>
     </row>
     <row r="112">
@@ -621,42 +621,42 @@
     </row>
     <row r="113">
       <c r="A113" s="0">
-        <v>-7.1123662515049091e-17</v>
+        <v>-4.8572257327350599e-17</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0">
-        <v>-0.011510242739589834</v>
+        <v>-0.011510242739589822</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0">
-        <v>6.7654215563095477e-17</v>
+        <v>6.5052130349130266e-17</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0">
-        <v>-2.8944325854746951e-16</v>
+        <v>-2.8924965101666853e-16</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0">
-        <v>4.7618159415563355e-16</v>
+        <v>4.7791631763161035e-16</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0">
-        <v>-0.010716432895479775</v>
+        <v>-0.010716432895479765</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0">
-        <v>-5.3256010712487978e-16</v>
+        <v>-5.2041704279304213e-16</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0">
-        <v>0.031584400803761556</v>
+        <v>0.031584400803761577</v>
       </c>
     </row>
     <row r="121">
@@ -1266,7 +1266,7 @@
     </row>
     <row r="242">
       <c r="A242" s="0">
-        <v>3.0159289474461981</v>
+        <v>3.0159289474461968</v>
       </c>
     </row>
     <row r="243">
@@ -1276,17 +1276,17 @@
     </row>
     <row r="244">
       <c r="A244" s="0">
-        <v>3.015928947446187</v>
+        <v>3.0159289474461861</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0">
-        <v>-9.2909655215394551</v>
+        <v>-9.2909655215394569</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0">
-        <v>3.0159289474462105</v>
+        <v>3.0159289474462123</v>
       </c>
     </row>
     <row r="247">
@@ -1296,17 +1296,17 @@
     </row>
     <row r="248">
       <c r="A248" s="0">
-        <v>3.0159289474462194</v>
+        <v>3.0159289474462239</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0">
-        <v>-9.296599213549797</v>
+        <v>-9.2965992135498006</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0">
-        <v>3.0159289474461444</v>
+        <v>3.0159289474461461</v>
       </c>
     </row>
     <row r="251">
@@ -1316,7 +1316,7 @@
     </row>
     <row r="252">
       <c r="A252" s="0">
-        <v>3.0159289474463113</v>
+        <v>3.0159289474463136</v>
       </c>
     </row>
     <row r="253">
@@ -1326,7 +1326,7 @@
     </row>
     <row r="254">
       <c r="A254" s="0">
-        <v>3.0159289474461044</v>
+        <v>3.0159289474461026</v>
       </c>
     </row>
     <row r="255">
@@ -1336,12 +1336,12 @@
     </row>
     <row r="256">
       <c r="A256" s="0">
-        <v>3.0159289474461741</v>
+        <v>3.015928947446175</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="0">
-        <v>-9.2984093469193834</v>
+        <v>-9.2984093469193798</v>
       </c>
     </row>
     <row r="258">
@@ -1351,7 +1351,7 @@
     </row>
     <row r="259">
       <c r="A259" s="0">
-        <v>-9.2985499379299625</v>
+        <v>-9.2985499379299696</v>
       </c>
     </row>
     <row r="260">
@@ -1366,37 +1366,37 @@
     </row>
     <row r="262">
       <c r="A262" s="0">
-        <v>3.0159289474458304</v>
+        <v>3.0159289474458362</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="0">
-        <v>-9.2987291538182451</v>
+        <v>-9.2987291538182379</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="0">
-        <v>3.0159289474462549</v>
+        <v>3.0159289474462567</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0">
-        <v>-9.2987883053024021</v>
+        <v>-9.2987883053024056</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0">
-        <v>3.0159289474458943</v>
+        <v>3.015928947445897</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0">
-        <v>-9.298834805617723</v>
+        <v>-9.2988348056177195</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="0">
-        <v>3.0159289474456266</v>
+        <v>3.015928947445627</v>
       </c>
     </row>
     <row r="269">
@@ -1406,37 +1406,37 @@
     </row>
     <row r="270">
       <c r="A270" s="0">
-        <v>3.0159289474464659</v>
+        <v>3.0159289474464566</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="0">
-        <v>-9.2989022688537908</v>
+        <v>-9.2989022688537926</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0">
-        <v>3.015928947446187</v>
+        <v>3.015928947446183</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="0">
-        <v>-9.2989271854552182</v>
+        <v>-9.29892718545522</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="0">
-        <v>3.0159289474459512</v>
+        <v>3.0159289474459436</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="0">
-        <v>-9.2989479539500284</v>
+        <v>-9.2989479539500373</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="0">
-        <v>3.0159289474462287</v>
+        <v>3.0159289474462265</v>
       </c>
     </row>
     <row r="277">
@@ -1446,27 +1446,27 @@
     </row>
     <row r="278">
       <c r="A278" s="0">
-        <v>3.0159289474464579</v>
+        <v>3.015928947446461</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0">
-        <v>-9.2989803175291268</v>
+        <v>-9.2989803175291339</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0">
-        <v>3.015928947445607</v>
+        <v>3.0159289474456004</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0">
-        <v>-9.2989930658519881</v>
+        <v>-9.2989930658519917</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0">
-        <v>3.0159289474452149</v>
+        <v>3.0159289474452144</v>
       </c>
     </row>
     <row r="283">
@@ -1481,22 +1481,22 @@
     </row>
     <row r="285">
       <c r="A285" s="0">
-        <v>-9.2990136529829588</v>
+        <v>-9.2990136529829606</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0">
-        <v>3.01592894744521</v>
+        <v>3.0159289474452193</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0">
-        <v>-9.2990220326579145</v>
+        <v>-9.2990220326579109</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0">
-        <v>3.0159289474460125</v>
+        <v>3.0159289474460156</v>
       </c>
     </row>
     <row r="289">
@@ -1506,57 +1506,57 @@
     </row>
     <row r="290">
       <c r="A290" s="0">
-        <v>3.0159289474449782</v>
+        <v>3.0159289474449817</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0">
-        <v>-9.2990359315455358</v>
+        <v>-9.299035931545534</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0">
-        <v>3.0159289474457522</v>
+        <v>3.0159289474457536</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="0">
-        <v>-9.29904173119224</v>
+        <v>-9.2990417311922418</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="0">
-        <v>3.0159289474469091</v>
+        <v>3.0159289474469055</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="0">
-        <v>-9.2990469097253801</v>
+        <v>-9.2990469097253783</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="0">
-        <v>3.0159289474474398</v>
+        <v>3.0159289474474407</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="0">
-        <v>-9.2990515527694999</v>
+        <v>-9.2990515527694946</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="0">
-        <v>3.0159289474451358</v>
+        <v>3.0159289474451372</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="0">
-        <v>-9.2990557316948603</v>
+        <v>-9.2990557316948586</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="0">
-        <v>3.0159289474454232</v>
+        <v>3.0159289474454183</v>
       </c>
     </row>
     <row r="301">
@@ -2166,7 +2166,7 @@
     </row>
     <row r="422">
       <c r="A422" s="0">
-        <v>-3.0159289474461981</v>
+        <v>-3.0159289474461968</v>
       </c>
     </row>
     <row r="423">
@@ -2176,17 +2176,17 @@
     </row>
     <row r="424">
       <c r="A424" s="0">
-        <v>-3.015928947446187</v>
+        <v>-3.0159289474461861</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="0">
-        <v>9.2909655215394551</v>
+        <v>9.2909655215394569</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="0">
-        <v>-3.0159289474462105</v>
+        <v>-3.0159289474462123</v>
       </c>
     </row>
     <row r="427">
@@ -2196,17 +2196,17 @@
     </row>
     <row r="428">
       <c r="A428" s="0">
-        <v>-3.0159289474462194</v>
+        <v>-3.0159289474462239</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="0">
-        <v>9.296599213549797</v>
+        <v>9.2965992135498006</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="0">
-        <v>-3.0159289474461444</v>
+        <v>-3.0159289474461461</v>
       </c>
     </row>
     <row r="431">
@@ -2216,7 +2216,7 @@
     </row>
     <row r="432">
       <c r="A432" s="0">
-        <v>-3.0159289474463113</v>
+        <v>-3.0159289474463136</v>
       </c>
     </row>
     <row r="433">
@@ -2226,7 +2226,7 @@
     </row>
     <row r="434">
       <c r="A434" s="0">
-        <v>-3.0159289474461044</v>
+        <v>-3.0159289474461026</v>
       </c>
     </row>
     <row r="435">
@@ -2236,12 +2236,12 @@
     </row>
     <row r="436">
       <c r="A436" s="0">
-        <v>-3.0159289474461741</v>
+        <v>-3.015928947446175</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="0">
-        <v>9.2984093469193834</v>
+        <v>9.2984093469193798</v>
       </c>
     </row>
     <row r="438">
@@ -2251,7 +2251,7 @@
     </row>
     <row r="439">
       <c r="A439" s="0">
-        <v>9.2985499379299625</v>
+        <v>9.2985499379299696</v>
       </c>
     </row>
     <row r="440">
@@ -2266,37 +2266,37 @@
     </row>
     <row r="442">
       <c r="A442" s="0">
-        <v>-3.0159289474458304</v>
+        <v>-3.0159289474458362</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="0">
-        <v>9.2987291538182451</v>
+        <v>9.2987291538182379</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="0">
-        <v>-3.0159289474462549</v>
+        <v>-3.0159289474462567</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="0">
-        <v>9.2987883053024021</v>
+        <v>9.2987883053024056</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="0">
-        <v>-3.0159289474458943</v>
+        <v>-3.015928947445897</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="0">
-        <v>9.298834805617723</v>
+        <v>9.2988348056177195</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="0">
-        <v>-3.0159289474456266</v>
+        <v>-3.015928947445627</v>
       </c>
     </row>
     <row r="449">
@@ -2306,37 +2306,37 @@
     </row>
     <row r="450">
       <c r="A450" s="0">
-        <v>-3.0159289474464659</v>
+        <v>-3.0159289474464566</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="0">
-        <v>9.2989022688537908</v>
+        <v>9.2989022688537926</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="0">
-        <v>-3.015928947446187</v>
+        <v>-3.015928947446183</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="0">
-        <v>9.2989271854552182</v>
+        <v>9.29892718545522</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="0">
-        <v>-3.0159289474459512</v>
+        <v>-3.0159289474459436</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="0">
-        <v>9.2989479539500284</v>
+        <v>9.2989479539500373</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="0">
-        <v>-3.0159289474462287</v>
+        <v>-3.0159289474462265</v>
       </c>
     </row>
     <row r="457">
@@ -2346,27 +2346,27 @@
     </row>
     <row r="458">
       <c r="A458" s="0">
-        <v>-3.0159289474464579</v>
+        <v>-3.015928947446461</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="0">
-        <v>9.2989803175291268</v>
+        <v>9.2989803175291339</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="0">
-        <v>-3.015928947445607</v>
+        <v>-3.0159289474456004</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="0">
-        <v>9.2989930658519881</v>
+        <v>9.2989930658519917</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="0">
-        <v>-3.0159289474452149</v>
+        <v>-3.0159289474452144</v>
       </c>
     </row>
     <row r="463">
@@ -2381,22 +2381,22 @@
     </row>
     <row r="465">
       <c r="A465" s="0">
-        <v>9.2990136529829588</v>
+        <v>9.2990136529829606</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="0">
-        <v>-3.01592894744521</v>
+        <v>-3.0159289474452193</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="0">
-        <v>9.2990220326579145</v>
+        <v>9.2990220326579109</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="0">
-        <v>-3.0159289474460125</v>
+        <v>-3.0159289474460156</v>
       </c>
     </row>
     <row r="469">
@@ -2406,57 +2406,57 @@
     </row>
     <row r="470">
       <c r="A470" s="0">
-        <v>-3.0159289474449782</v>
+        <v>-3.0159289474449817</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="0">
-        <v>9.2990359315455358</v>
+        <v>9.299035931545534</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="0">
-        <v>-3.0159289474457522</v>
+        <v>-3.0159289474457536</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="0">
-        <v>9.29904173119224</v>
+        <v>9.2990417311922418</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="0">
-        <v>-3.0159289474469091</v>
+        <v>-3.0159289474469055</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="0">
-        <v>9.2990469097253801</v>
+        <v>9.2990469097253783</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="0">
-        <v>-3.0159289474474398</v>
+        <v>-3.0159289474474407</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="0">
-        <v>9.2990515527694999</v>
+        <v>9.2990515527694946</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="0">
-        <v>-3.0159289474451358</v>
+        <v>-3.0159289474451372</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="0">
-        <v>9.2990557316948603</v>
+        <v>9.2990557316948586</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="0">
-        <v>-3.0159289474454232</v>
+        <v>-3.0159289474454183</v>
       </c>
     </row>
     <row r="481">
@@ -3066,7 +3066,7 @@
     </row>
     <row r="602">
       <c r="A602" s="0">
-        <v>3.0159289474461981</v>
+        <v>3.0159289474461968</v>
       </c>
     </row>
     <row r="603">
@@ -3076,17 +3076,17 @@
     </row>
     <row r="604">
       <c r="A604" s="0">
-        <v>3.015928947446187</v>
+        <v>3.0159289474461861</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="0">
-        <v>-9.2909655215394551</v>
+        <v>-9.2909655215394569</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="0">
-        <v>3.0159289474462105</v>
+        <v>3.0159289474462123</v>
       </c>
     </row>
     <row r="607">
@@ -3096,17 +3096,17 @@
     </row>
     <row r="608">
       <c r="A608" s="0">
-        <v>3.0159289474462194</v>
+        <v>3.0159289474462239</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" s="0">
-        <v>-9.296599213549797</v>
+        <v>-9.2965992135498006</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" s="0">
-        <v>3.0159289474461444</v>
+        <v>3.0159289474461461</v>
       </c>
     </row>
     <row r="611">
@@ -3116,7 +3116,7 @@
     </row>
     <row r="612">
       <c r="A612" s="0">
-        <v>3.0159289474463113</v>
+        <v>3.0159289474463136</v>
       </c>
     </row>
     <row r="613">
@@ -3126,7 +3126,7 @@
     </row>
     <row r="614">
       <c r="A614" s="0">
-        <v>3.0159289474461044</v>
+        <v>3.0159289474461026</v>
       </c>
     </row>
     <row r="615">
@@ -3136,12 +3136,12 @@
     </row>
     <row r="616">
       <c r="A616" s="0">
-        <v>3.0159289474461741</v>
+        <v>3.015928947446175</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" s="0">
-        <v>-9.2984093469193834</v>
+        <v>-9.2984093469193798</v>
       </c>
     </row>
     <row r="618">
@@ -3151,7 +3151,7 @@
     </row>
     <row r="619">
       <c r="A619" s="0">
-        <v>-9.2985499379299625</v>
+        <v>-9.2985499379299696</v>
       </c>
     </row>
     <row r="620">
@@ -3166,37 +3166,37 @@
     </row>
     <row r="622">
       <c r="A622" s="0">
-        <v>3.0159289474458304</v>
+        <v>3.0159289474458362</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" s="0">
-        <v>-9.2987291538182451</v>
+        <v>-9.2987291538182379</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" s="0">
-        <v>3.0159289474462549</v>
+        <v>3.0159289474462567</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" s="0">
-        <v>-9.2987883053024021</v>
+        <v>-9.2987883053024056</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" s="0">
-        <v>3.0159289474458943</v>
+        <v>3.015928947445897</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" s="0">
-        <v>-9.298834805617723</v>
+        <v>-9.2988348056177195</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" s="0">
-        <v>3.0159289474456266</v>
+        <v>3.015928947445627</v>
       </c>
     </row>
     <row r="629">
@@ -3206,37 +3206,37 @@
     </row>
     <row r="630">
       <c r="A630" s="0">
-        <v>3.0159289474464659</v>
+        <v>3.0159289474464566</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" s="0">
-        <v>-9.2989022688537908</v>
+        <v>-9.2989022688537926</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" s="0">
-        <v>3.015928947446187</v>
+        <v>3.015928947446183</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" s="0">
-        <v>-9.2989271854552182</v>
+        <v>-9.29892718545522</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" s="0">
-        <v>3.0159289474459512</v>
+        <v>3.0159289474459436</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" s="0">
-        <v>-9.2989479539500284</v>
+        <v>-9.2989479539500373</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" s="0">
-        <v>3.0159289474462287</v>
+        <v>3.0159289474462265</v>
       </c>
     </row>
     <row r="637">
@@ -3246,27 +3246,27 @@
     </row>
     <row r="638">
       <c r="A638" s="0">
-        <v>3.0159289474464579</v>
+        <v>3.015928947446461</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" s="0">
-        <v>-9.2989803175291268</v>
+        <v>-9.2989803175291339</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" s="0">
-        <v>3.015928947445607</v>
+        <v>3.0159289474456004</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" s="0">
-        <v>-9.2989930658519881</v>
+        <v>-9.2989930658519917</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" s="0">
-        <v>3.0159289474452149</v>
+        <v>3.0159289474452144</v>
       </c>
     </row>
     <row r="643">
@@ -3281,22 +3281,22 @@
     </row>
     <row r="645">
       <c r="A645" s="0">
-        <v>-9.2990136529829588</v>
+        <v>-9.2990136529829606</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" s="0">
-        <v>3.01592894744521</v>
+        <v>3.0159289474452193</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" s="0">
-        <v>-9.2990220326579145</v>
+        <v>-9.2990220326579109</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" s="0">
-        <v>3.0159289474460125</v>
+        <v>3.0159289474460156</v>
       </c>
     </row>
     <row r="649">
@@ -3306,57 +3306,57 @@
     </row>
     <row r="650">
       <c r="A650" s="0">
-        <v>3.0159289474449782</v>
+        <v>3.0159289474449817</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" s="0">
-        <v>-9.2990359315455358</v>
+        <v>-9.299035931545534</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" s="0">
-        <v>3.0159289474457522</v>
+        <v>3.0159289474457536</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" s="0">
-        <v>-9.29904173119224</v>
+        <v>-9.2990417311922418</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" s="0">
-        <v>3.0159289474469091</v>
+        <v>3.0159289474469055</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" s="0">
-        <v>-9.2990469097253801</v>
+        <v>-9.2990469097253783</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" s="0">
-        <v>3.0159289474474398</v>
+        <v>3.0159289474474407</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" s="0">
-        <v>-9.2990515527694999</v>
+        <v>-9.2990515527694946</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" s="0">
-        <v>3.0159289474451358</v>
+        <v>3.0159289474451372</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" s="0">
-        <v>-9.2990557316948603</v>
+        <v>-9.2990557316948586</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" s="0">
-        <v>3.0159289474454232</v>
+        <v>3.0159289474454183</v>
       </c>
     </row>
     <row r="661">
@@ -3366,7 +3366,7 @@
     </row>
     <row r="662">
       <c r="A662" s="0">
-        <v>-3.0159289474461981</v>
+        <v>-3.0159289474461968</v>
       </c>
     </row>
     <row r="663">
@@ -3376,17 +3376,17 @@
     </row>
     <row r="664">
       <c r="A664" s="0">
-        <v>-3.015928947446187</v>
+        <v>-3.0159289474461861</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" s="0">
-        <v>9.2909655215394551</v>
+        <v>9.2909655215394569</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" s="0">
-        <v>-3.0159289474462105</v>
+        <v>-3.0159289474462123</v>
       </c>
     </row>
     <row r="667">
@@ -3396,17 +3396,17 @@
     </row>
     <row r="668">
       <c r="A668" s="0">
-        <v>-3.0159289474462194</v>
+        <v>-3.0159289474462239</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" s="0">
-        <v>9.296599213549797</v>
+        <v>9.2965992135498006</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" s="0">
-        <v>-3.0159289474461444</v>
+        <v>-3.0159289474461461</v>
       </c>
     </row>
     <row r="671">
@@ -3416,7 +3416,7 @@
     </row>
     <row r="672">
       <c r="A672" s="0">
-        <v>-3.0159289474463113</v>
+        <v>-3.0159289474463136</v>
       </c>
     </row>
     <row r="673">
@@ -3426,7 +3426,7 @@
     </row>
     <row r="674">
       <c r="A674" s="0">
-        <v>-3.0159289474461044</v>
+        <v>-3.0159289474461026</v>
       </c>
     </row>
     <row r="675">
@@ -3436,12 +3436,12 @@
     </row>
     <row r="676">
       <c r="A676" s="0">
-        <v>-3.0159289474461741</v>
+        <v>-3.015928947446175</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" s="0">
-        <v>9.2984093469193834</v>
+        <v>9.2984093469193798</v>
       </c>
     </row>
     <row r="678">
@@ -3451,7 +3451,7 @@
     </row>
     <row r="679">
       <c r="A679" s="0">
-        <v>9.2985499379299625</v>
+        <v>9.2985499379299696</v>
       </c>
     </row>
     <row r="680">
@@ -3466,37 +3466,37 @@
     </row>
     <row r="682">
       <c r="A682" s="0">
-        <v>-3.0159289474458304</v>
+        <v>-3.0159289474458362</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" s="0">
-        <v>9.2987291538182451</v>
+        <v>9.2987291538182379</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" s="0">
-        <v>-3.0159289474462549</v>
+        <v>-3.0159289474462567</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" s="0">
-        <v>9.2987883053024021</v>
+        <v>9.2987883053024056</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" s="0">
-        <v>-3.0159289474458943</v>
+        <v>-3.015928947445897</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" s="0">
-        <v>9.298834805617723</v>
+        <v>9.2988348056177195</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" s="0">
-        <v>-3.0159289474456266</v>
+        <v>-3.015928947445627</v>
       </c>
     </row>
     <row r="689">
@@ -3506,37 +3506,37 @@
     </row>
     <row r="690">
       <c r="A690" s="0">
-        <v>-3.0159289474464659</v>
+        <v>-3.0159289474464566</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" s="0">
-        <v>9.2989022688537908</v>
+        <v>9.2989022688537926</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" s="0">
-        <v>-3.015928947446187</v>
+        <v>-3.015928947446183</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" s="0">
-        <v>9.2989271854552182</v>
+        <v>9.29892718545522</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" s="0">
-        <v>-3.0159289474459512</v>
+        <v>-3.0159289474459436</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" s="0">
-        <v>9.2989479539500284</v>
+        <v>9.2989479539500373</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" s="0">
-        <v>-3.0159289474462287</v>
+        <v>-3.0159289474462265</v>
       </c>
     </row>
     <row r="697">
@@ -3546,27 +3546,27 @@
     </row>
     <row r="698">
       <c r="A698" s="0">
-        <v>-3.0159289474464579</v>
+        <v>-3.015928947446461</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" s="0">
-        <v>9.2989803175291268</v>
+        <v>9.2989803175291339</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" s="0">
-        <v>-3.015928947445607</v>
+        <v>-3.0159289474456004</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" s="0">
-        <v>9.2989930658519881</v>
+        <v>9.2989930658519917</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" s="0">
-        <v>-3.0159289474452149</v>
+        <v>-3.0159289474452144</v>
       </c>
     </row>
     <row r="703">
@@ -3581,22 +3581,22 @@
     </row>
     <row r="705">
       <c r="A705" s="0">
-        <v>9.2990136529829588</v>
+        <v>9.2990136529829606</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" s="0">
-        <v>-3.01592894744521</v>
+        <v>-3.0159289474452193</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" s="0">
-        <v>9.2990220326579145</v>
+        <v>9.2990220326579109</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" s="0">
-        <v>-3.0159289474460125</v>
+        <v>-3.0159289474460156</v>
       </c>
     </row>
     <row r="709">
@@ -3606,57 +3606,57 @@
     </row>
     <row r="710">
       <c r="A710" s="0">
-        <v>-3.0159289474449782</v>
+        <v>-3.0159289474449817</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" s="0">
-        <v>9.2990359315455358</v>
+        <v>9.299035931545534</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" s="0">
-        <v>-3.0159289474457522</v>
+        <v>-3.0159289474457536</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" s="0">
-        <v>9.29904173119224</v>
+        <v>9.2990417311922418</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" s="0">
-        <v>-3.0159289474469091</v>
+        <v>-3.0159289474469055</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" s="0">
-        <v>9.2990469097253801</v>
+        <v>9.2990469097253783</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" s="0">
-        <v>-3.0159289474474398</v>
+        <v>-3.0159289474474407</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" s="0">
-        <v>9.2990515527694999</v>
+        <v>9.2990515527694946</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" s="0">
-        <v>-3.0159289474451358</v>
+        <v>-3.0159289474451372</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" s="0">
-        <v>9.2990557316948603</v>
+        <v>9.2990557316948586</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" s="0">
-        <v>-3.0159289474454232</v>
+        <v>-3.0159289474454183</v>
       </c>
     </row>
     <row r="721">
